--- a/output/(山本)目的適合性_目的合致性_再構成.xlsx
+++ b/output/(山本)目的適合性_目的合致性_再構成.xlsx
@@ -461,13 +461,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>文書の各構成単位（章、節、項、図表）において、定義された適用範囲を逸脱せず、次工程で決定すべき実装詳細や目的外の情報を含めずに、対象読者が求める適切な抽象度で記述している。</t>
+          <t>開発工程ごとの定義書（要求定義書や基本設計書など）の役割定義に基づき、当該工程で決定すべきスコープに合致した要件のみを記述し、次工程以降で検討すべき実装の技術的詳細を排除している。</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>【非適合例】要件定義書において、プログラムの内部変数名や具体的なソートアルゴリズムなどの実装詳細を記述している（次工程の設計で決定すべき情報が含まれている）。
-→【適合例】要件定義書では、ビジネス上の制約と達成すべき機能要件に絞って記述し、具体的な実現方式は設計工程の担当範囲として分離している。</t>
+          <t>★新規追加
+【非適合例】要求定義書の画面要件において、ボタンの配置座標は（x:120,y:340）とし、Reactの標準コンポーネントを使用して実装する。（次工程の詳細設計および実装工程で決定すべき技術的詳細を含んでおり、要求定義の目的を逸脱しているため。）
+→【適合例】要求定義書の画面要件において、ユーザーが入力内容を確定してサーバーへ送信するための「登録」ボタンを配置する。</t>
         </is>
       </c>
     </row>
@@ -479,13 +480,14 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>文書の目的を完遂するために、読み手が意思決定や次の行動（承認、作業開始等）を行う際の判断材料となる、具体的な条件、数値、期限、成果物の定義を漏れなく記述している。</t>
+          <t>課題管理票や進捗報告書において、ステークホルダーに意思決定を要求する場合、判断の根拠となる遅延などの発生事象、希望する期限、および要求事項を定量的な数値を用いて明記している。</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>【非適合例】進捗遅延の報告において、遅延の理由のみを記載し、挽回策の提示や新たな納期への合意を求める期限を記載していない。
-→【適合例】進捗遅延の報告において、現状の課題を説明した上で、修正後の希望納期とそれに対する合意の可否をいつまでに回答してほしいかを明記している。</t>
+          <t>★新規追加
+【非適合例】外部APIの仕様変更対応により、結合テスト工程の開発進捗が遅延している。（日程変更の承認を得る目的において、遅延日数や希望する延期日程などの定量的な判断材料が欠落しているため。）
+→【適合例】外部APIの仕様変更対応により、結合テスト工程が予定より5日遅延している。これを踏まえ、リリース判定会議の日程を当初の10月15日から10月20日へ延期する承認を要求する。</t>
         </is>
       </c>
     </row>
@@ -497,14 +499,14 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>個別の仕様やデータの羅列を行う前に、それらを選択・構成した論理的根拠や判断の拠り所となる上位の設計方針、アーキテクチャの選定意図、または前提条件を定義している。</t>
+          <t>方式設計書や基本設計書において、技術要素を採用した結論だけでなく、その決定に至った背景となるシステム特性、非機能要件、および上位設計方針との適合性を明記している。</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>★新規追加
-【非適合例】基本設計書において、個別の機能説明のみが並んでおり、システム全体で統一すべきエラーハンドリングの方針やセキュリティの考え方が記述されていない。
-→【適合例】基本設計書の共通事項として、システム全体の「可用性を最優先する」という設計方針を明記し、それに基づく冗長化構成の判断基準を記述している。</t>
+【非適合例】本システムのデータベースには、NoSQL型のドキュメント指向データベースを採用する。（特定の技術を選定した根拠となる非機能要件や上位設計方針との関連性が欠落しているため。）
+→【適合例】本システムは将来的なデータ構造の変更が頻繁に発生するシステム特性を持つため、スキーマの柔軟性と拡張性を重視する上位設計方針に基づき、データベースにはNoSQL型のドキュメント指向データベースを採用する。</t>
         </is>
       </c>
     </row>
